--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260624.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.34%</t>
+          <t>10.52%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.79%</t>
+          <t>9.73%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.78%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.70%</t>
+          <t>7.66%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>5.25%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.87%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.03%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>63,809</t>
+          <t>20,973</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,973</t>
+          <t>63,809</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -887,44 +887,44 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,385</t>
+          <t>26,303</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,303</t>
+          <t>24,385</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,745</t>
+          <t>50,896</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>50,896</t>
+          <t>9,745</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1254,51 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,343</t>
+          <t>11,522</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,522</t>
+          <t>14,343</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1452,46 +1452,46 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>27,902</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>27,902</t>
+          <t>14,528</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1518,29 +1518,29 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>14,528</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1716,9 +1716,23 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>102,226,578</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
